--- a/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
+++ b/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\ccs\BCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\ccs\BCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F268FE25-6FA1-4964-97BE-7705BD55074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D5070-3C15-40E1-AE61-02F08EE4A9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25785" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Source:</t>
   </si>
@@ -82,9 +82,6 @@
     <t>2022 to 2012 USD</t>
   </si>
   <si>
-    <t>This variable captures any BAU subsidies for CCS, specified in dollars per ton captured.</t>
-  </si>
-  <si>
     <t>BCS BAU CCS Subsidy</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Credit Value</t>
   </si>
   <si>
-    <t>For electricity, adjust the credit value based on its duration relative to the financing repayment period</t>
-  </si>
-  <si>
     <t>Years</t>
   </si>
   <si>
@@ -119,6 +113,9 @@
   </si>
   <si>
     <t>12 years</t>
+  </si>
+  <si>
+    <t>South Korea does not have a subsidy system for CCS (Carbon Capture and Storage)</t>
   </si>
 </sst>
 </file>
@@ -126,20 +123,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -147,8 +144,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -171,10 +182,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -183,13 +194,14 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="백분율" xfId="2" builtinId="5"/>
+    <cellStyle name="통화" xfId="1" builtinId="4"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -492,16 +504,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="55.88671875" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" customWidth="1"/>
+    <col min="1" max="1" width="30.375" customWidth="1"/>
+    <col min="2" max="2" width="55.875" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -518,15 +530,11 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="A6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>0.78500000000000003</v>
@@ -537,7 +545,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="6">
         <v>85</v>
@@ -545,13 +553,14 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -560,14 +569,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB35C55-7F27-44A6-A8A7-496D78F28576}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="7">
         <f>About!B11</f>
@@ -576,7 +585,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>20</v>
@@ -584,7 +593,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -592,7 +601,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7">
         <f>B1*B3/B2</f>
@@ -600,6 +609,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -610,15 +620,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2">
         <v>2021</v>
@@ -721,98 +731,88 @@
       <c r="C2" s="4">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="E2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="F2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="G2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="H2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="I2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="J2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="K2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="L2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="M2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -826,102 +826,93 @@
       <c r="C3" s="4">
         <v>0</v>
       </c>
-      <c r="D3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="E3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="F3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="G3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="H3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="I3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="J3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="K3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="L3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="M3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -932,11 +923,11 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1031,7 +1022,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -1154,6 +1145,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76EEE8E6-9E29-41FB-AA42-7A86BE820E0F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226F896D-BB2E-447D-A74E-6E1EEF393833}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94781E0A-71D3-4C72-91B2-0B5F4C52ACB1}"/>
 </file>
--- a/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
+++ b/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\ccs\BCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\ccs\BCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D5070-3C15-40E1-AE61-02F08EE4A9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BEB8B5-2238-4D76-99C4-AF6C48E10333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25785" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="768" windowWidth="23232" windowHeight="12828" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Electricity Calculations" sheetId="5" r:id="rId2"/>
-    <sheet name="BCS-BCS" sheetId="4" r:id="rId3"/>
-    <sheet name="BCS-DoSfCS" sheetId="6" r:id="rId4"/>
+    <sheet name="BCS-BCS" sheetId="4" r:id="rId2"/>
+    <sheet name="BCS-DoSfCS" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">About!$A$11</definedName>
@@ -62,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Source:</t>
   </si>
@@ -88,34 +87,22 @@
     <t>$ / metric ton</t>
   </si>
   <si>
-    <t>45Q Tax Credit Amount</t>
-  </si>
-  <si>
-    <t>Credit Amount</t>
-  </si>
-  <si>
-    <t>Repayment Period for Financing</t>
-  </si>
-  <si>
-    <t>45Q Credit Duration</t>
-  </si>
-  <si>
-    <t>Credit Value</t>
-  </si>
-  <si>
     <t>Years</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>45Q Duration</t>
-  </si>
-  <si>
-    <t>12 years</t>
-  </si>
-  <si>
     <t>South Korea does not have a subsidy system for CCS (Carbon Capture and Storage)</t>
+  </si>
+  <si>
+    <t>^evereything has been 0'd out</t>
+  </si>
+  <si>
+    <t>Length of time</t>
+  </si>
+  <si>
+    <t>irrelevant</t>
   </si>
 </sst>
 </file>
@@ -123,20 +110,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -144,20 +131,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -182,10 +169,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -194,14 +181,13 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="백분율" xfId="2" builtinId="5"/>
-    <cellStyle name="통화" xfId="1" builtinId="4"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -504,19 +490,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.375" customWidth="1"/>
-    <col min="2" max="2" width="55.875" customWidth="1"/>
-    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="55.88671875" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,18 +510,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>17</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="5">
         <v>0.78500000000000003</v>
       </c>
@@ -543,20 +533,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3"/>
       <c r="B11" s="6">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -567,45 +555,300 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB35C55-7F27-44A6-A8A7-496D78F28576}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AE3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="7">
-        <f>About!B11</f>
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="B1" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="2">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="2">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="2">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="2">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="2">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="2">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="2">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="2">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="2">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="2">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="2">
+        <v>2034</v>
+      </c>
+      <c r="P1" s="2">
+        <v>2035</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>2036</v>
+      </c>
+      <c r="R1" s="2">
+        <v>2037</v>
+      </c>
+      <c r="S1" s="2">
+        <v>2038</v>
+      </c>
+      <c r="T1" s="2">
+        <v>2039</v>
+      </c>
+      <c r="U1" s="2">
+        <v>2040</v>
+      </c>
+      <c r="V1" s="2">
+        <v>2041</v>
+      </c>
+      <c r="W1" s="2">
+        <v>2042</v>
+      </c>
+      <c r="X1" s="2">
+        <v>2043</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>2044</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>2045</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>2046</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>2047</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>2048</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>2049</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7">
-        <f>B1*B3/B2</f>
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -615,319 +858,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2">
-        <v>2021</v>
-      </c>
-      <c r="C1" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D1" s="2">
-        <v>2023</v>
-      </c>
-      <c r="E1" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F1" s="2">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="2">
-        <v>2026</v>
-      </c>
-      <c r="H1" s="2">
-        <v>2027</v>
-      </c>
-      <c r="I1" s="2">
-        <v>2028</v>
-      </c>
-      <c r="J1" s="2">
-        <v>2029</v>
-      </c>
-      <c r="K1" s="2">
-        <v>2030</v>
-      </c>
-      <c r="L1" s="2">
-        <v>2031</v>
-      </c>
-      <c r="M1" s="2">
-        <v>2032</v>
-      </c>
-      <c r="N1" s="2">
-        <v>2033</v>
-      </c>
-      <c r="O1" s="2">
-        <v>2034</v>
-      </c>
-      <c r="P1" s="2">
-        <v>2035</v>
-      </c>
-      <c r="Q1" s="2">
-        <v>2036</v>
-      </c>
-      <c r="R1" s="2">
-        <v>2037</v>
-      </c>
-      <c r="S1" s="2">
-        <v>2038</v>
-      </c>
-      <c r="T1" s="2">
-        <v>2039</v>
-      </c>
-      <c r="U1" s="2">
-        <v>2040</v>
-      </c>
-      <c r="V1" s="2">
-        <v>2041</v>
-      </c>
-      <c r="W1" s="2">
-        <v>2042</v>
-      </c>
-      <c r="X1" s="2">
-        <v>2043</v>
-      </c>
-      <c r="Y1" s="2">
-        <v>2044</v>
-      </c>
-      <c r="Z1" s="2">
-        <v>2045</v>
-      </c>
-      <c r="AA1" s="2">
-        <v>2046</v>
-      </c>
-      <c r="AB1" s="2">
-        <v>2047</v>
-      </c>
-      <c r="AC1" s="2">
-        <v>2048</v>
-      </c>
-      <c r="AD1" s="2">
-        <v>2049</v>
-      </c>
-      <c r="AE1" s="2">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
-        <v>0</v>
-      </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4">
-        <v>0</v>
-      </c>
-      <c r="W2" s="4">
-        <v>0</v>
-      </c>
-      <c r="X2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5698252-CD29-4D86-9D7F-2214C5598602}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1020,128 +960,128 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:AE2" si="0">$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1151,6 +1091,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1294,29 +1249,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76EEE8E6-9E29-41FB-AA42-7A86BE820E0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226F896D-BB2E-447D-A74E-6E1EEF393833}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226F896D-BB2E-447D-A74E-6E1EEF393833}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94781E0A-71D3-4C72-91B2-0B5F4C52ACB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94781E0A-71D3-4C72-91B2-0B5F4C52ACB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76EEE8E6-9E29-41FB-AA42-7A86BE820E0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>